--- a/Result/profitability/3338.xlsx
+++ b/Result/profitability/3338.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM65"/>
+  <dimension ref="A1:AM66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2375</v>
+        <v>0.20375</v>
       </c>
       <c r="N2" t="n">
-        <v>18.67375</v>
+        <v>18.195</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08750000000000002</v>
+        <v>-0.001250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.675</v>
+        <v>17.3775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.22</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.17875</v>
+        <v>-0.23</v>
       </c>
       <c r="N4" t="n">
-        <v>16.75875</v>
+        <v>16.39125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.25625</v>
+        <v>-0.2925</v>
       </c>
       <c r="N5" t="n">
-        <v>16.38375</v>
+        <v>16.06</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.30375</v>
+        <v>-0.3225</v>
       </c>
       <c r="N6" t="n">
-        <v>16.20625</v>
+        <v>16.1775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.31875</v>
+        <v>-0.3375</v>
       </c>
       <c r="N7" t="n">
-        <v>16.13</v>
+        <v>15.5675</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8683,6 +8683,133 @@
       </c>
       <c r="AM65" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D66" t="n">
+        <v>854</v>
+      </c>
+      <c r="E66" t="n">
+        <v>174</v>
+      </c>
+      <c r="F66" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="G66" t="n">
+        <v>23</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J66" t="n">
+        <v>20</v>
+      </c>
+      <c r="K66" t="n">
+        <v>17</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="N66" t="n">
+        <v>19.245</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-0.2592592592592593</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>-0.1080084299262382</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-0.5918367346938775</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>-0.1326844262295082</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
